--- a/checklist_forms/009_food_defense_assessment_template--checklist_forms.xlsx
+++ b/checklist_forms/009_food_defense_assessment_template--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>food_control_measures</t>
+          <t>food_control_measures_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Food Control Measures</t>
+          <t>Food Control Measures 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>food_recalled_quantity</t>
+          <t>food_recalled_quantity_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quantity of Food Recalled</t>
+          <t>Food Recalled Quantity 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_other</t>
+          <t>food_recalled_quantity_other_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Food Recalled Quantity Other 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>recall_date</t>
+          <t>recall_date_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Recall Date</t>
+          <t>Recall Date 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>food_control_measures_choices</t>
+          <t>food_control_measures_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2030,7 +2030,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>food_control_measures_choices</t>
+          <t>food_control_measures_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>food_control_measures_choices</t>
+          <t>food_control_measures_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_choices</t>
+          <t>food_recalled_quantity_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_choices</t>
+          <t>food_recalled_quantity_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_choices</t>
+          <t>food_recalled_quantity_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_choices</t>
+          <t>food_recalled_quantity_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2166,7 +2166,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>food_recalled_quantity_choices</t>
+          <t>food_recalled_quantity_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
